--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07244399999999999</v>
+        <v>0.061875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.067217</v>
+        <v>0.059742</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06408800000000001</v>
+        <v>0.05526</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004262</v>
+        <v>-0.002989</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.004094</v>
+        <v>-0.003626</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.766024</v>
+        <v>0.626995</v>
       </c>
       <c r="C3" t="n">
-        <v>0.408942</v>
+        <v>0.316348</v>
       </c>
       <c r="D3" t="n">
-        <v>0.38559</v>
+        <v>0.298671</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.332446</v>
+        <v>-0.298557</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.047988</v>
+        <v>-0.029766</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.865683</v>
+        <v>0.770159</v>
       </c>
       <c r="C4" t="n">
-        <v>0.646491</v>
+        <v>0.376774</v>
       </c>
       <c r="D4" t="n">
-        <v>0.601285</v>
+        <v>0.35213</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.19389</v>
+        <v>-0.377166</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.070508</v>
+        <v>-0.040864</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.061875</v>
+        <v>0.063027</v>
       </c>
       <c r="C2" t="n">
-        <v>0.059742</v>
+        <v>0.060566</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05526</v>
+        <v>0.057513</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.002989</v>
+        <v>-0.002656</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.003626</v>
+        <v>-0.002858</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.626995</v>
+        <v>0.63491</v>
       </c>
       <c r="C3" t="n">
-        <v>0.316348</v>
+        <v>0.285902</v>
       </c>
       <c r="D3" t="n">
-        <v>0.298671</v>
+        <v>0.280086</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.298557</v>
+        <v>-0.328867</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.029766</v>
+        <v>-0.025957</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.770159</v>
+        <v>0.774709</v>
       </c>
       <c r="C4" t="n">
-        <v>0.376774</v>
+        <v>0.379013</v>
       </c>
       <c r="D4" t="n">
-        <v>0.35213</v>
+        <v>0.357118</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.377166</v>
+        <v>-0.380331</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.040864</v>
+        <v>-0.03726</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.063027</v>
+        <v>0.066471</v>
       </c>
       <c r="C2" t="n">
-        <v>0.060566</v>
+        <v>0.062128</v>
       </c>
       <c r="D2" t="n">
-        <v>0.057513</v>
+        <v>0.057505</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.002656</v>
+        <v>-0.004175</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.002858</v>
+        <v>-0.004791</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.63491</v>
+        <v>0.654959</v>
       </c>
       <c r="C3" t="n">
-        <v>0.285902</v>
+        <v>0.36452</v>
       </c>
       <c r="D3" t="n">
-        <v>0.280086</v>
+        <v>0.339415</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.328867</v>
+        <v>-0.275218</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.025957</v>
+        <v>-0.040326</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.774709</v>
+        <v>0.744555</v>
       </c>
       <c r="C4" t="n">
-        <v>0.379013</v>
+        <v>0.416501</v>
       </c>
       <c r="D4" t="n">
-        <v>0.357118</v>
+        <v>0.388032</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.380331</v>
+        <v>-0.304124</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.03726</v>
+        <v>-0.0524</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.066471</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.062128</v>
+        <v>0.060279</v>
       </c>
       <c r="D2" t="n">
-        <v>0.057505</v>
+        <v>0.0559</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004175</v>
+        <v>-0.004115</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.004791</v>
+        <v>-0.004628</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.654959</v>
+        <v>0.67306</v>
       </c>
       <c r="C3" t="n">
-        <v>0.36452</v>
+        <v>0.362386</v>
       </c>
       <c r="D3" t="n">
-        <v>0.339415</v>
+        <v>0.335623</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.275218</v>
+        <v>-0.291572</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.040326</v>
+        <v>-0.045865</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.744555</v>
+        <v>0.742665</v>
       </c>
       <c r="C4" t="n">
-        <v>0.416501</v>
+        <v>0.415006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.388032</v>
+        <v>0.384908</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.304124</v>
+        <v>-0.301576</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0524</v>
+        <v>-0.056181</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.061748</v>
       </c>
       <c r="C2" t="n">
-        <v>0.060279</v>
+        <v>0.05464</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0559</v>
+        <v>0.051469</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004115</v>
+        <v>-0.00634</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.004628</v>
+        <v>-0.003939</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.67306</v>
+        <v>0.673009</v>
       </c>
       <c r="C3" t="n">
-        <v>0.362386</v>
+        <v>0.271034</v>
       </c>
       <c r="D3" t="n">
-        <v>0.335623</v>
+        <v>0.25364</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.291572</v>
+        <v>-0.371062</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.045865</v>
+        <v>-0.048306</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.742665</v>
+        <v>0.741044</v>
       </c>
       <c r="C4" t="n">
-        <v>0.415006</v>
+        <v>0.342605</v>
       </c>
       <c r="D4" t="n">
-        <v>0.384908</v>
+        <v>0.314223</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.301576</v>
+        <v>-0.364482</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.056181</v>
+        <v>-0.06234</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.061748</v>
+        <v>0.061784</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05464</v>
+        <v>0.054734</v>
       </c>
       <c r="D2" t="n">
-        <v>0.051469</v>
+        <v>0.04982</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.00634</v>
+        <v>-0.006211</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.003939</v>
+        <v>-0.005753</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.673009</v>
+        <v>0.672434</v>
       </c>
       <c r="C3" t="n">
-        <v>0.271034</v>
+        <v>0.260935</v>
       </c>
       <c r="D3" t="n">
-        <v>0.25364</v>
+        <v>0.230509</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.371062</v>
+        <v>-0.361453</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.048306</v>
+        <v>-0.080472</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.741044</v>
+        <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.342605</v>
+        <v>0.307991</v>
       </c>
       <c r="D4" t="n">
-        <v>0.314223</v>
+        <v>0.277584</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.364482</v>
+        <v>-0.351095</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06234</v>
+        <v>-0.082659</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -458,16 +458,16 @@
         <v>0.061784</v>
       </c>
       <c r="C2" t="n">
-        <v>0.054734</v>
+        <v>0.054782</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04982</v>
+        <v>0.050274</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.006211</v>
+        <v>-0.00609</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.005753</v>
+        <v>-0.005421</v>
       </c>
     </row>
     <row r="3">
@@ -480,16 +480,16 @@
         <v>0.672434</v>
       </c>
       <c r="C3" t="n">
-        <v>0.260935</v>
+        <v>0.262011</v>
       </c>
       <c r="D3" t="n">
-        <v>0.230509</v>
+        <v>0.232207</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.361453</v>
+        <v>-0.363831</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.080472</v>
+        <v>-0.07639600000000001</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.307991</v>
+        <v>0.310576</v>
       </c>
       <c r="D4" t="n">
-        <v>0.277584</v>
+        <v>0.279905</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.351095</v>
+        <v>-0.351245</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.082659</v>
+        <v>-0.080188</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.061784</v>
+        <v>0.061712</v>
       </c>
       <c r="C2" t="n">
-        <v>0.054782</v>
+        <v>0.055705</v>
       </c>
       <c r="D2" t="n">
-        <v>0.050274</v>
+        <v>0.055705</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.00609</v>
+        <v>-0.006007</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.005421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -480,16 +480,16 @@
         <v>0.672434</v>
       </c>
       <c r="C3" t="n">
-        <v>0.262011</v>
+        <v>0.265808</v>
       </c>
       <c r="D3" t="n">
-        <v>0.232207</v>
+        <v>0.265808</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.363831</v>
+        <v>-0.406626</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.07639600000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.310576</v>
+        <v>0.30141</v>
       </c>
       <c r="D4" t="n">
-        <v>0.279905</v>
+        <v>0.30141</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.351245</v>
+        <v>-0.409928</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.080188</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.061712</v>
+        <v>0.060827</v>
       </c>
       <c r="C2" t="n">
-        <v>0.055705</v>
+        <v>0.055481</v>
       </c>
       <c r="D2" t="n">
-        <v>0.055705</v>
+        <v>0.055481</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.006007</v>
+        <v>-0.005346</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.672434</v>
+        <v>0.634074</v>
       </c>
       <c r="C3" t="n">
-        <v>0.265808</v>
+        <v>0.264434</v>
       </c>
       <c r="D3" t="n">
-        <v>0.265808</v>
+        <v>0.264434</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.406626</v>
+        <v>-0.369639</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -502,13 +502,13 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.30141</v>
+        <v>0.298916</v>
       </c>
       <c r="D4" t="n">
-        <v>0.30141</v>
+        <v>0.298916</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.409928</v>
+        <v>-0.412422</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -458,13 +458,13 @@
         <v>0.060827</v>
       </c>
       <c r="C2" t="n">
-        <v>0.055481</v>
+        <v>0.055231</v>
       </c>
       <c r="D2" t="n">
-        <v>0.055481</v>
+        <v>0.055231</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.005346</v>
+        <v>-0.005596</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.634074</v>
+        <v>0.620194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.264434</v>
+        <v>0.260987</v>
       </c>
       <c r="D3" t="n">
-        <v>0.264434</v>
+        <v>0.260987</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.369639</v>
+        <v>-0.359208</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -502,13 +502,13 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.298916</v>
+        <v>0.295407</v>
       </c>
       <c r="D4" t="n">
-        <v>0.298916</v>
+        <v>0.295407</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.412422</v>
+        <v>-0.415931</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -458,13 +458,13 @@
         <v>0.060827</v>
       </c>
       <c r="C2" t="n">
-        <v>0.055231</v>
+        <v>0.055216</v>
       </c>
       <c r="D2" t="n">
-        <v>0.055231</v>
+        <v>0.055216</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.005596</v>
+        <v>-0.005611</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -480,13 +480,13 @@
         <v>0.620194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.260987</v>
+        <v>0.257932</v>
       </c>
       <c r="D3" t="n">
-        <v>0.260987</v>
+        <v>0.257932</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.359208</v>
+        <v>-0.362263</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -502,13 +502,13 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.295407</v>
+        <v>0.295159</v>
       </c>
       <c r="D4" t="n">
-        <v>0.295407</v>
+        <v>0.295159</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.415931</v>
+        <v>-0.416179</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
       <c r="C2" t="n">
-        <v>0.055216</v>
+        <v>0.055168</v>
       </c>
       <c r="D2" t="n">
-        <v>0.055216</v>
+        <v>0.055168</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.005611</v>
+        <v>-0.005714</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -480,13 +480,13 @@
         <v>0.620194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.257932</v>
+        <v>0.256726</v>
       </c>
       <c r="D3" t="n">
-        <v>0.257932</v>
+        <v>0.256726</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.362263</v>
+        <v>-0.363469</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -502,13 +502,13 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.295159</v>
+        <v>0.295054</v>
       </c>
       <c r="D4" t="n">
-        <v>0.295159</v>
+        <v>0.295054</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.416179</v>
+        <v>-0.416284</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.060882</v>
+        <v>0.059367</v>
       </c>
       <c r="C2" t="n">
-        <v>0.055168</v>
+        <v>0.054584</v>
       </c>
       <c r="D2" t="n">
-        <v>0.055168</v>
+        <v>0.054584</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.005714</v>
+        <v>-0.004783</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -480,13 +480,13 @@
         <v>0.620194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.256726</v>
+        <v>0.263619</v>
       </c>
       <c r="D3" t="n">
-        <v>0.256726</v>
+        <v>0.263619</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.363469</v>
+        <v>-0.356576</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -502,13 +502,13 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.295054</v>
+        <v>0.330368</v>
       </c>
       <c r="D4" t="n">
-        <v>0.295054</v>
+        <v>0.330368</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.416284</v>
+        <v>-0.380969</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -458,13 +458,13 @@
         <v>0.059367</v>
       </c>
       <c r="C2" t="n">
-        <v>0.054584</v>
+        <v>0.054603</v>
       </c>
       <c r="D2" t="n">
-        <v>0.054584</v>
+        <v>0.054603</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004783</v>
+        <v>-0.004765</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -480,13 +480,13 @@
         <v>0.620194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.263619</v>
+        <v>0.263815</v>
       </c>
       <c r="D3" t="n">
-        <v>0.263619</v>
+        <v>0.263815</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.356576</v>
+        <v>-0.356379</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -502,13 +502,13 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.330368</v>
+        <v>0.33048</v>
       </c>
       <c r="D4" t="n">
-        <v>0.330368</v>
+        <v>0.33048</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.380969</v>
+        <v>-0.380857</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.059367</v>
+        <v>0.058745</v>
       </c>
       <c r="C2" t="n">
-        <v>0.054603</v>
+        <v>0.054064</v>
       </c>
       <c r="D2" t="n">
-        <v>0.054603</v>
+        <v>0.054064</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004765</v>
+        <v>-0.004681</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -480,13 +480,13 @@
         <v>0.620194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.263815</v>
+        <v>0.266966</v>
       </c>
       <c r="D3" t="n">
-        <v>0.263815</v>
+        <v>0.266966</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.356379</v>
+        <v>-0.353228</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -502,13 +502,13 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.33048</v>
+        <v>0.334027</v>
       </c>
       <c r="D4" t="n">
-        <v>0.33048</v>
+        <v>0.334027</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.380857</v>
+        <v>-0.37731</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
       <c r="C2" t="n">
-        <v>0.054064</v>
+        <v>0.054413</v>
       </c>
       <c r="D2" t="n">
-        <v>0.054064</v>
+        <v>0.054413</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004681</v>
+        <v>-0.004424</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -480,13 +480,13 @@
         <v>0.620194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.266966</v>
+        <v>0.267257</v>
       </c>
       <c r="D3" t="n">
-        <v>0.266966</v>
+        <v>0.267257</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.353228</v>
+        <v>-0.352938</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -502,13 +502,13 @@
         <v>0.711338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.334027</v>
+        <v>0.334312</v>
       </c>
       <c r="D4" t="n">
-        <v>0.334027</v>
+        <v>0.334312</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.37731</v>
+        <v>-0.377026</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,16 +455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.058836</v>
+        <v>0.058745</v>
       </c>
       <c r="C2" t="n">
-        <v>0.054413</v>
+        <v>0.054108</v>
       </c>
       <c r="D2" t="n">
-        <v>0.054413</v>
+        <v>0.054108</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004424</v>
+        <v>-0.004638</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.620194</v>
+        <v>0.6049369999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.267257</v>
+        <v>0.276042</v>
       </c>
       <c r="D3" t="n">
-        <v>0.267257</v>
+        <v>0.276042</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.352938</v>
+        <v>-0.328895</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -499,16 +499,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.711338</v>
+        <v>0.672434</v>
       </c>
       <c r="C4" t="n">
-        <v>0.334312</v>
+        <v>0.3424</v>
       </c>
       <c r="D4" t="n">
-        <v>0.334312</v>
+        <v>0.3424</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.377026</v>
+        <v>-0.330034</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
